--- a/bakup/customers/mohammad javad.xlsx
+++ b/bakup/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="196">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -621,6 +621,12 @@
   </si>
   <si>
     <t>کوصشریات</t>
+  </si>
+  <si>
+    <t>1405/05/30</t>
+  </si>
+  <si>
+    <t>ابمیوه کیک چسپس</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1132,7 @@
       </c>
       <c r="H2" s="8">
         <f>B161</f>
-        <v>646500</v>
+        <v>866500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3313,17 +3319,23 @@
     <row r="156" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <f t="shared" si="7"/>
-        <v>646500</v>
-      </c>
-      <c r="B156" s="7"/>
+        <v>866500</v>
+      </c>
+      <c r="B156" s="7">
+        <v>220000</v>
+      </c>
       <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="1"/>
+      <c r="D156" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>646500</v>
+        <v>866500</v>
       </c>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3333,7 +3345,7 @@
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>646500</v>
+        <v>866500</v>
       </c>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3344,7 +3356,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>13061500</v>
+        <v>13281500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3356,7 +3368,7 @@
     <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>646500</v>
+        <v>866500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>
